--- a/questionari/risposte/Edinburgh Test Hand Dominance - VISIONARY (Responses).xlsx
+++ b/questionari/risposte/Edinburgh Test Hand Dominance - VISIONARY (Responses).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="24">
   <si>
     <t>Timestamp</t>
   </si>
@@ -47,12 +47,51 @@
   </si>
   <si>
     <t>Open a box (hand lifting the lid)</t>
+  </si>
+  <si>
+    <t>S001</t>
+  </si>
+  <si>
+    <t>Right hand (strong preference)</t>
+  </si>
+  <si>
+    <t>Right hand</t>
+  </si>
+  <si>
+    <t>Indifferent/Both</t>
+  </si>
+  <si>
+    <t>S002</t>
+  </si>
+  <si>
+    <t>S003</t>
+  </si>
+  <si>
+    <t>S004</t>
+  </si>
+  <si>
+    <t>Left hand</t>
+  </si>
+  <si>
+    <t>S005</t>
+  </si>
+  <si>
+    <t>S006</t>
+  </si>
+  <si>
+    <t>Left hand (strong preference)</t>
+  </si>
+  <si>
+    <t>S007</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="10.0"/>
@@ -80,12 +119,24 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -166,27 +217,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:L1" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L8" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="12">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
-    <tableColumn name="Column3" id="3"/>
-    <tableColumn name="Column4" id="4"/>
-    <tableColumn name="Column5" id="5"/>
-    <tableColumn name="Column6" id="6"/>
-    <tableColumn name="Column7" id="7"/>
-    <tableColumn name="Column8" id="8"/>
-    <tableColumn name="Column9" id="9"/>
-    <tableColumn name="Column10" id="10"/>
-    <tableColumn name="Column11" id="11"/>
-    <tableColumn name="Column12" id="12"/>
+    <tableColumn name="Timestamp" id="1"/>
+    <tableColumn name="ID" id="2"/>
+    <tableColumn name="Writing" id="3"/>
+    <tableColumn name="Drawing" id="4"/>
+    <tableColumn name="Throwing" id="5"/>
+    <tableColumn name="Scissors" id="6"/>
+    <tableColumn name="Toothbrush" id="7"/>
+    <tableColumn name="Knife (without a fork)" id="8"/>
+    <tableColumn name="Spoon" id="9"/>
+    <tableColumn name="Broom (hand positioned high on the handle)" id="10"/>
+    <tableColumn name="Striking match (hand rubbing the match)" id="11"/>
+    <tableColumn name="Open a box (hand lifting the lid)" id="12"/>
   </tableColumns>
   <tableStyleInfo name="Form Responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" headerRowCount="1"/>
-    </ext>
-  </extLst>
 </table>
 </file>
 
@@ -438,6 +484,272 @@
         <v>11</v>
       </c>
     </row>
+    <row r="2" ht="22.5" customHeight="1">
+      <c r="A2" s="2">
+        <v>46294.76438436343</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="4">
+        <v>46295.38729893518</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="4">
+        <v>46295.455277175926</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="4">
+        <v>46295.5048866088</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="4">
+        <v>46295.61263373843</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="4">
+        <v>46295.673880601855</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="4">
+        <v>46295.721829016205</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
   <tableParts count="1">

--- a/questionari/risposte/Edinburgh Test Hand Dominance - VISIONARY (Responses).xlsx
+++ b/questionari/risposte/Edinburgh Test Hand Dominance - VISIONARY (Responses).xlsx
@@ -201,7 +201,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:L7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:L12" headerRowCount="1">
   <tableColumns count="12">
     <tableColumn id="1" name="Timestamp"/>
     <tableColumn id="2" name="ID"/>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.88" customWidth="1" style="6" min="1" max="7"/>
@@ -854,7 +854,306 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1" s="6"/>
+    <row r="8" ht="22.5" customHeight="1" s="6">
+      <c r="A8" s="4" t="n">
+        <v>46296.43380547454</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>S007</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Indifferent/Both</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Indifferent/Both</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Indifferent/Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1" s="6">
+      <c r="A9" s="4" t="n">
+        <v>46296.49612587963</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>S008</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Left hand</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1" s="6">
+      <c r="A10" s="4" t="n">
+        <v>46296.58566054398</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>S009</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1" s="6">
+      <c r="A11" s="4" t="n">
+        <v>46296.64122185185</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>S010</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1" s="6">
+      <c r="A12" s="4" t="n">
+        <v>46296.6905272338</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>S011</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Left hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Left hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Right hand (strong preference)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Indifferent/Both</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Right hand</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Indifferent/Both</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/questionari/risposte/Edinburgh Test Hand Dominance - VISIONARY (Responses).xlsx
+++ b/questionari/risposte/Edinburgh Test Hand Dominance - VISIONARY (Responses).xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.88" customWidth="1" style="6" min="1" max="7"/>
@@ -856,7 +856,7 @@
     </row>
     <row r="8" ht="22.5" customHeight="1" s="6">
       <c r="A8" s="4" t="n">
-        <v>46296.43380547454</v>
+        <v>46296.49612587963</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Right hand (strong preference)</t>
+          <t>Right hand</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Right hand (strong preference)</t>
+          <t>Right hand</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Indifferent/Both</t>
+          <t>Right hand</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Right hand</t>
+          <t>Left hand</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Indifferent/Both</t>
+          <t>Right hand</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -905,18 +905,18 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>Right hand (strong preference)</t>
+          <t>Right hand</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Indifferent/Both</t>
+          <t>Right hand</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1" s="6">
       <c r="A9" s="4" t="n">
-        <v>46296.49612587963</v>
+        <v>46296.58566054398</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -925,12 +925,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Right hand</t>
+          <t>Right hand (strong preference)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Right hand</t>
+          <t>Right hand (strong preference)</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -940,43 +940,43 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Right hand</t>
+          <t>Right hand (strong preference)</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Right hand</t>
+          <t>Right hand (strong preference)</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Left hand</t>
+          <t>Right hand (strong preference)</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Right hand</t>
+          <t>Right hand (strong preference)</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Right hand</t>
+          <t>Right hand (strong preference)</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Right hand</t>
+          <t>Right hand (strong preference)</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Right hand</t>
+          <t>Right hand (strong preference)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1" s="6">
       <c r="A10" s="4" t="n">
-        <v>46296.58566054398</v>
+        <v>46296.64122185185</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Right hand</t>
+          <t>Right hand (strong preference)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1036,7 +1036,7 @@
     </row>
     <row r="11" ht="22.5" customHeight="1" s="6">
       <c r="A11" s="4" t="n">
-        <v>46296.64122185185</v>
+        <v>46296.6905272338</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Right hand (strong preference)</t>
+          <t>Left hand (strong preference)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Right hand (strong preference)</t>
+          <t>Left hand (strong preference)</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1060,100 +1060,41 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Right hand (strong preference)</t>
+          <t>Right hand</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Right hand (strong preference)</t>
+          <t>Right hand</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Right hand (strong preference)</t>
+          <t>Right hand</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Right hand (strong preference)</t>
+          <t>Right hand</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Right hand (strong preference)</t>
+          <t>Indifferent/Both</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>Right hand (strong preference)</t>
+          <t>Right hand</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>Right hand (strong preference)</t>
+          <t>Indifferent/Both</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="22.5" customHeight="1" s="6">
-      <c r="A12" s="4" t="n">
-        <v>46296.6905272338</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>S011</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Left hand (strong preference)</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Left hand (strong preference)</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Right hand (strong preference)</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Right hand</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Right hand</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>Right hand</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>Right hand</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>Indifferent/Both</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>Right hand</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>Indifferent/Both</t>
-        </is>
-      </c>
-    </row>
+    <row r="12" ht="22.5" customHeight="1" s="6"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
